--- a/data/trans_orig/IP07C11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31541</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46819</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61940</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>40574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108649</t>
+          <t>109754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>130502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134016</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154880</t>
+          <t>154398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248608</t>
+          <t>248128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278988</t>
+          <t>278374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50322</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71757</t>
+          <t>71246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53495</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74408</t>
+          <t>76084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110723</t>
+          <t>111508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140163</t>
+          <t>138904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25668</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23245</t>
+          <t>23493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35040</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52873</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68764</t>
+          <t>68466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>23561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163826</t>
+          <t>163944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190766</t>
+          <t>191355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187027</t>
+          <t>188840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213376</t>
+          <t>214901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362426</t>
+          <t>361287</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>399259</t>
+          <t>398761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85997</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111720</t>
+          <t>112731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83593</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109153</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>174038</t>
+          <t>174295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>210663</t>
+          <t>211281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32575</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>28223</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>38889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52081</t>
+          <t>52923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68232</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41444</t>
+          <t>40119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115423</t>
+          <t>115680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138380</t>
+          <t>137587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137089</t>
+          <t>136663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159995</t>
+          <t>159946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259140</t>
+          <t>260069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291759</t>
+          <t>292013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57196</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79127</t>
+          <t>78671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>55265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77707</t>
+          <t>77078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115903</t>
+          <t>118785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148216</t>
+          <t>149327</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,77 +4732,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1189</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>33217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44291</t>
+          <t>44479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69691</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86598</t>
+          <t>86465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27290</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29289</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46051</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185963</t>
+          <t>184454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214592</t>
+          <t>212799</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200874</t>
+          <t>201709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229545</t>
+          <t>228517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>395745</t>
+          <t>396382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433429</t>
+          <t>434294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>90141</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116282</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>86717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>112985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>184366</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>222057</t>
+          <t>220176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24598</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43794</t>
+          <t>43235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31872</t>
+          <t>32099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143579</t>
+          <t>144212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168952</t>
+          <t>167948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137288</t>
+          <t>135488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286915</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322182</t>
+          <t>322256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>60168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84175</t>
+          <t>83766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65394</t>
+          <t>64516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89360</t>
+          <t>90100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133690</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166781</t>
+          <t>166993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>22113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35330</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49229</t>
+          <t>49058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50262</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62675</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90311</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108997</t>
+          <t>108805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18018</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23988</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198021</t>
+          <t>199921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229982</t>
+          <t>231024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209830</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239751</t>
+          <t>241555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419028</t>
+          <t>417892</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>461240</t>
+          <t>460562</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>94567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196382</t>
+          <t>197385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237216</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la menor en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28399</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22997</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33220</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26090</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20322</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31284</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20276</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30981</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28399</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23426</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32717</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,7%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61310</t>
+          <t>61537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14146</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9251</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18665</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13682</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24502</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14150</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24648</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,25%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14146</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19507</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26377</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40574</t>
+          <t>40426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1259</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4410</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4885</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>143893</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132792</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>154505</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>120314</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>109754</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>130502</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>108786</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>130264</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>143893</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>131970</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>154398</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248128</t>
+          <t>247720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278374</t>
+          <t>278134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64075</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52660</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>60480</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50458</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71246</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>50941</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64075</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54244</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76084</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111508</t>
+          <t>111118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138904</t>
+          <t>139486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9347</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5445</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15286</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8286</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4856</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13684</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4896</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13295</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,35%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5248</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15312</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3931</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>217314</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>217314</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>217314</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>217314</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>217314</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>217314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29109</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23368</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34745</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>32015</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25864</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37385</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>25721</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37771</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29109</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23493</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34732</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>59,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51455</t>
+          <t>52678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68466</t>
+          <t>68612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -2204,67 +2204,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12209</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23276</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>18518</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13456</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24033</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13003</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24866</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>17679</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>12441</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23561</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28504</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44858</t>
+          <t>44074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -2317,67 +2317,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>2326</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6676</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,29%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1387</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4840</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4857</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>201401</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>187307</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>215193</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>65,06%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>60,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>69,51%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>178419</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>163944</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>191355</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>164984</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>190548</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>61,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>201401</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>188840</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>214901</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>361287</t>
+          <t>361010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398761</t>
+          <t>399290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>95899</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>81845</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>108829</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>97663</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>84056</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>112731</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>86188</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>110904</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>33,6%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>28,92%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>95899</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>83714</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>107395</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>174295</t>
+          <t>175400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>211281</t>
+          <t>211890</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2999,67 +2999,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>12278</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7583</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>18743</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>11871</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>7267</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>18828</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>7158</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>17978</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>12278</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>7637</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>19343</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32621</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2693</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6709</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la menor en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26815</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20951</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32391</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33833</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28223</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38889</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28019</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39163</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>65,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26815</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21175</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32133</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>52803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17490</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12221</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23731</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14796</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9675</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19844</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20960</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17490</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12415</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23224</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40119</t>
+          <t>39575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2997</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7130</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,8%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>149210</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137811</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>160459</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>126833</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>115680</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>137587</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>115577</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>137741</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>149210</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>136663</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>159946</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260069</t>
+          <t>260432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292013</t>
+          <t>290014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -4476,74 +4476,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65483</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54722</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77230</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67607</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57390</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78671</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56852</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78657</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>28,46%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>39,38%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65483</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55265</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77078</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>193</t>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118785</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149327</t>
+          <t>149261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9492</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5373</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15509</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4700</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9238</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9241</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9492</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5212</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15469</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21223</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -4707,102 +4707,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1189</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38922</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44129</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39206</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32450</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44781</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32850</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44359</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,48%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>38922</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>33217</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44479</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69804</t>
+          <t>68912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86465</t>
+          <t>86106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16508</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11300</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22335</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20880</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15494</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27611</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15662</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>27337</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16508</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11126</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21841</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29101</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>46786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -5276,102 +5276,102 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3649</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>715</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3809</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>5052</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1437</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>5032</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>214946</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>200528</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>228504</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>65,92%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,08%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>199871</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>184454</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>212799</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>184623</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>214475</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>64,03%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59,09%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>214946</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>201709</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>228517</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>65,92%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396382</t>
+          <t>393849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434294</t>
+          <t>434326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>99481</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>87275</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>113454</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>34,79%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>103282</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>90141</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>117949</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>90072</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>118549</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>33,08%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>99481</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>86717</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>112985</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181294</t>
+          <t>184648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>220176</t>
+          <t>224352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11071</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>17418</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>14264</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>14338</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>11071</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>6455</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>17524</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6071,102 +6071,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3087</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1189</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4221</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>312174</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la menor en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19860</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14697</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24790</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16968</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12340</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21635</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12516</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21471</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19860</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14756</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24590</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>42981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14578</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10137</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19868</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11124</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6815</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15805</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15744</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14578</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9610</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19366</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>31944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -6871,67 +6871,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5874</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,2%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -7092,107 +7092,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4349</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148979</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137055</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>161090</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>155638</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>144212</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>167948</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>141425</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>166834</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148979</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135488</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>161142</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287020</t>
+          <t>288026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322256</t>
+          <t>322313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,09%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76974</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65677</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88616</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72620</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60168</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83766</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>61839</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86132</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76974</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64516</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>90100</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133695</t>
+          <t>133159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166993</t>
+          <t>165790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10351</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17006</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14514</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9586</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22113</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9254</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21200</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10351</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16033</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>17893</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -7666,102 +7666,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2843</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4146</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4648</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4826</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56954</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49865</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>62634</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>42575</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35839</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>49058</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34896</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>49128</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>56954</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>49959</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>62500</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89825</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>108664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17024</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11156</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23853</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>22,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24325</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17851</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30789</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17933</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32327</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>17024</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11830</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>24007</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51257</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3398</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7152</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7059</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5794</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4735</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>225793</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>209981</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>240816</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>60,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>215180</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>199921</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>231024</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>201611</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>231219</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>62,37%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>57,94%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>66,96%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>225793</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>209938</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>241555</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417892</t>
+          <t>419518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>460562</t>
+          <t>462181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>108576</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>93579</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>124195</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,8%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>108069</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>93947</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>122777</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>91762</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>121233</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>31,32%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>108576</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>94567</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>124415</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197385</t>
+          <t>195624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>238737</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14074</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8350</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>20503</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19809</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13411</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>27143</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14156</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>28208</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>14074</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>8664</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>21082</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>45412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1356</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -9138,107 +9138,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3663</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>345032</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>345032</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>345032</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
